--- a/exam_forms/010_electric_potential_and_capacitance_quiz--exam_forms.xlsx
+++ b/exam_forms/010_electric_potential_and_capacitance_quiz--exam_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -863,12 +863,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>electric_potential_and_capacitance_quiz_help</t>
+          <t>electric_potential_and_capacitance_quiz_help_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>electric potential and capacitance quiz help</t>
+          <t>Electric Potential And Capacitance Quiz Help 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>electric_potential_and_capacitance_quiz_result_2</t>
+          <t>electric_potential_and_capacitance_quiz_result_2_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>electric potential and capacitance quiz result 2</t>
+          <t>Electric Potential And Capacitance Quiz Result 2 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>electric_potential_and_capacitance_quiz_submission</t>
+          <t>electric_potential_and_capacitance_quiz_submission_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>electric potential and capacitance quiz submission</t>
+          <t>Electric Potential And Capacitance Quiz Submission 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>electric_potential_and_capacitance_quiz_result</t>
+          <t>electric_potential_and_capacitance_quiz_result_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>electric potential and capacitance quiz result</t>
+          <t>Electric Potential And Capacitance Quiz Result 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
